--- a/case-studies/kestrel-valley-cycle/data/quickbooks/Journal_2026-07.xlsx
+++ b/case-studies/kestrel-valley-cycle/data/quickbooks/Journal_2026-07.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:K38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,7 +444,7 @@
     <row r="5">
       <c r="B5" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Transaction date</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -464,12 +464,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Memo/Description</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Account</t>
+          <t>Account Name</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -484,7 +484,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Create date</t>
+          <t>Created on</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -494,170 +494,188 @@
       </c>
     </row>
     <row r="6">
-      <c r="B6" t="inlineStr">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1102</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
         <is>
           <t>07/01/2026</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Transfer</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Payroll funding</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>10200 Payroll Checking</t>
-        </is>
-      </c>
-      <c r="H6" s="1" t="n">
-        <v>40000</v>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>4429</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Payroll Checking</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Transfer to payroll</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>10900 Transfers Clearing</t>
+        </is>
+      </c>
+      <c r="H7" s="1" t="n">
+        <v>25000</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>07/01/2026 10:15:00 AM</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Dana Merritt</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
         <is>
           <t>07/01/2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Dana Merritt</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Payroll funding</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>4429</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Payroll Checking</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Transfer to payroll</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
         <is>
           <t>10100 Checking - First Prairie</t>
         </is>
       </c>
-      <c r="I7" s="1" t="n">
-        <v>40000</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="H8" s="1" t="n">
-        <v>40000</v>
-      </c>
       <c r="I8" s="1" t="n">
-        <v>40000</v>
+        <v>25000</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>07/01/2026 10:15:00 AM</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Dana Merritt</t>
+        </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>07/01/2026</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Check</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>4429</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Payroll Checking</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Transfer to payroll</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>10900 Transfers Clearing</t>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Total for 1102</t>
         </is>
       </c>
       <c r="H9" s="1" t="n">
         <v>25000</v>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="I9" s="1" t="n">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
         <is>
           <t>07/01/2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Dana Merritt</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Transfer to payroll</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>10100 Checking - First Prairie</t>
-        </is>
-      </c>
-      <c r="I10" s="1" t="n">
-        <v>25000</v>
-      </c>
-    </row>
-    <row r="11">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Transfer</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Payroll funding</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>10200 Payroll Checking</t>
+        </is>
+      </c>
       <c r="H11" s="1" t="n">
-        <v>25000</v>
-      </c>
-      <c r="I11" s="1" t="n">
-        <v>25000</v>
+        <v>40000</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>07/01/2026 10:15:00 AM</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Dana Merritt</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>07/01/2026</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Journal Entry</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>1071</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Cycle Tech Legal</t>
-        </is>
-      </c>
+          <t>Transfer</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Settle distributor dispute (claim from March 2026)</t>
+          <t>Payroll funding</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>68000 Professional Fees</t>
-        </is>
-      </c>
-      <c r="H12" s="1" t="n">
-        <v>30000</v>
+          <t>10100 Checking - First Prairie</t>
+        </is>
+      </c>
+      <c r="I12" s="1" t="n">
+        <v>40000</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>07/01/2026 10:15:00 AM</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -667,26 +685,23 @@
       </c>
     </row>
     <row r="13">
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Settle distributor dispute (claim from March 2026)</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>20000 Accounts Payable (A/P)</t>
-        </is>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Total for 1101</t>
+        </is>
+      </c>
+      <c r="H13" s="1" t="n">
+        <v>40000</v>
       </c>
       <c r="I13" s="1" t="n">
-        <v>30000</v>
+        <v>40000</v>
       </c>
     </row>
     <row r="14">
-      <c r="H14" s="1" t="n">
-        <v>30000</v>
-      </c>
-      <c r="I14" s="1" t="n">
-        <v>30000</v>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>1106</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -717,16 +732,28 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
+          <t>07/08/2026 10:15:00 AM</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Dana Merritt</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
           <t>07/08/2026</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>Dana Merritt</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Deposit</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>Customer receipts</t>
@@ -740,8 +767,23 @@
       <c r="I16" s="1" t="n">
         <v>33580.9</v>
       </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>07/08/2026 10:15:00 AM</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Dana Merritt</t>
+        </is>
+      </c>
     </row>
     <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Total for 1106</t>
+        </is>
+      </c>
       <c r="H17" s="1" t="n">
         <v>33580.9</v>
       </c>
@@ -750,219 +792,447 @@
       </c>
     </row>
     <row r="18">
-      <c r="B18" t="inlineStr">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>1103</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>07/08/2026</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Journal Entry</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>1071</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Cycle Tech Legal</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Settle distributor dispute (claim from March 2026)</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>68000 Professional Fees</t>
+        </is>
+      </c>
+      <c r="H19" s="1" t="n">
+        <v>30000</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>07/08/2026 10:15:00 AM</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Dana Merritt</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>07/08/2026</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Journal Entry</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1071</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Cycle Tech Legal</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Settle distributor dispute (claim from March 2026)</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>20000 Accounts Payable (A/P)</t>
+        </is>
+      </c>
+      <c r="I20" s="1" t="n">
+        <v>30000</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>07/08/2026 10:15:00 AM</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Dana Merritt</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Total for 1103</t>
+        </is>
+      </c>
+      <c r="H21" s="1" t="n">
+        <v>30000</v>
+      </c>
+      <c r="I21" s="1" t="n">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>1104</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
         <is>
           <t>07/10/2026</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>Check</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>4431</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>Big Timber Office Supply</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>Supplies</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>67000 Office Supplies</t>
         </is>
       </c>
-      <c r="H18" s="1" t="n">
+      <c r="H23" s="1" t="n">
         <v>2215</v>
       </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>07/10/2026</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>Dana Merritt</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Supplies</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>10100 Checking - First Prairie</t>
-        </is>
-      </c>
-      <c r="I19" s="1" t="n">
-        <v>2215</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="H20" s="1" t="n">
-        <v>2215</v>
-      </c>
-      <c r="I20" s="1" t="n">
-        <v>2215</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>07/14/2026</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Deposit</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Customer receipts</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>10100 Checking - First Prairie</t>
-        </is>
-      </c>
-      <c r="H21" s="1" t="n">
-        <v>27904.15</v>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>07/14/2026</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>Dana Merritt</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Customer receipts</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>11000 Accounts Receivable (A/R)</t>
-        </is>
-      </c>
-      <c r="I22" s="1" t="n">
-        <v>27904.15</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="H23" s="1" t="n">
-        <v>27904.15</v>
-      </c>
-      <c r="I23" s="1" t="n">
-        <v>27904.15</v>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>07/10/2026 10:15:00 AM</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Dana Merritt</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" t="inlineStr">
         <is>
+          <t>07/10/2026</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>4431</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Big Timber Office Supply</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Supplies</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>10100 Checking - First Prairie</t>
+        </is>
+      </c>
+      <c r="I24" s="1" t="n">
+        <v>2215</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>07/10/2026 10:15:00 AM</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Dana Merritt</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Total for 1104</t>
+        </is>
+      </c>
+      <c r="H25" s="1" t="n">
+        <v>2215</v>
+      </c>
+      <c r="I25" s="1" t="n">
+        <v>2215</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>07/14/2026</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Deposit</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Customer receipts</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>10100 Checking - First Prairie</t>
+        </is>
+      </c>
+      <c r="H27" s="1" t="n">
+        <v>27904.15</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>07/14/2026 10:15:00 AM</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Dana Merritt</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>07/14/2026</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Deposit</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Customer receipts</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>11000 Accounts Receivable (A/R)</t>
+        </is>
+      </c>
+      <c r="I28" s="1" t="n">
+        <v>27904.15</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>07/14/2026 10:15:00 AM</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Dana Merritt</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Total for 1107</t>
+        </is>
+      </c>
+      <c r="H29" s="1" t="n">
+        <v>27904.15</v>
+      </c>
+      <c r="I29" s="1" t="n">
+        <v>27904.15</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>1105</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="inlineStr">
+        <is>
           <t>07/15/2026</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>Check</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>4433</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>Velo Freight Lines</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>June freight (invoice VF-0630)</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>66000 Freight Out</t>
         </is>
       </c>
-      <c r="H24" s="1" t="n">
+      <c r="H31" s="1" t="n">
         <v>6100</v>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>07/15/2026 10:15:00 AM</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Dana Merritt</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="inlineStr">
         <is>
           <t>07/15/2026</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>Dana Merritt</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="F25" t="inlineStr">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>4433</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Velo Freight Lines</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
         <is>
           <t>June freight (invoice VF-0630)</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>10100 Checking - First Prairie</t>
         </is>
       </c>
-      <c r="I25" s="1" t="n">
+      <c r="I32" s="1" t="n">
         <v>6100</v>
       </c>
-    </row>
-    <row r="26">
-      <c r="H26" s="1" t="n">
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>07/15/2026 10:15:00 AM</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Dana Merritt</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Total for 1105</t>
+        </is>
+      </c>
+      <c r="H33" s="1" t="n">
         <v>6100</v>
       </c>
-      <c r="I26" s="1" t="n">
+      <c r="I33" s="1" t="n">
         <v>6100</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="H27" s="1" t="n">
+      <c r="H34" s="1" t="n">
         <v>164800.05</v>
       </c>
-      <c r="I27" s="1" t="n">
+      <c r="I34" s="1" t="n">
         <v>164800.05</v>
       </c>
     </row>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>Accrual Basis Friday, July 24, 2026 09:05 AM GMTZ</t>
         </is>

--- a/case-studies/kestrel-valley-cycle/data/quickbooks/Journal_2026-07.xlsx
+++ b/case-studies/kestrel-valley-cycle/data/quickbooks/Journal_2026-07.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K38"/>
+  <dimension ref="A1:K54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -513,26 +513,26 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4429</t>
+          <t>4427</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Payroll Checking</t>
+          <t>Members</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Transfer to payroll</t>
+          <t>Member distribution</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>10900 Transfers Clearing</t>
+          <t>31000 Members' Distributions</t>
         </is>
       </c>
       <c r="H7" s="1" t="n">
-        <v>25000</v>
+        <v>7500</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -558,17 +558,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4429</t>
+          <t>4427</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Payroll Checking</t>
+          <t>Members</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Transfer to payroll</t>
+          <t>Member distribution</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="I8" s="1" t="n">
-        <v>25000</v>
+        <v>7500</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -597,16 +597,16 @@
         </is>
       </c>
       <c r="H9" s="1" t="n">
-        <v>25000</v>
+        <v>7500</v>
       </c>
       <c r="I9" s="1" t="n">
-        <v>25000</v>
+        <v>7500</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1101</t>
+          <t>1103</t>
         </is>
       </c>
     </row>
@@ -618,23 +618,31 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Transfer</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
+          <t>Check</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>4428</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Hyalite Fabrication</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Payroll funding</t>
+          <t>Display fixture repair</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>10200 Payroll Checking</t>
+          <t>67000 Office Supplies</t>
         </is>
       </c>
       <c r="H11" s="1" t="n">
-        <v>40000</v>
+        <v>640</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -655,14 +663,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Transfer</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
+          <t>Check</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>4428</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Hyalite Fabrication</t>
+        </is>
+      </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Payroll funding</t>
+          <t>Display fixture repair</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -671,7 +687,7 @@
         </is>
       </c>
       <c r="I12" s="1" t="n">
-        <v>40000</v>
+        <v>640</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -687,52 +703,60 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total for 1101</t>
+          <t>Total for 1103</t>
         </is>
       </c>
       <c r="H13" s="1" t="n">
-        <v>40000</v>
+        <v>640</v>
       </c>
       <c r="I13" s="1" t="n">
-        <v>40000</v>
+        <v>640</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1106</t>
+          <t>1104</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>07/01/2026</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Deposit</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
+          <t>Check</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>4429</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Payroll Checking</t>
+        </is>
+      </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Customer receipts</t>
+          <t>Transfer to payroll</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>10100 Checking - First Prairie</t>
+          <t>10900 Transfers Clearing</t>
         </is>
       </c>
       <c r="H15" s="1" t="n">
-        <v>33580.9</v>
+        <v>25000</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>07/08/2026 10:15:00 AM</t>
+          <t>07/01/2026 10:15:00 AM</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -744,32 +768,40 @@
     <row r="16">
       <c r="B16" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>07/01/2026</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Deposit</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
+          <t>Check</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>4429</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Payroll Checking</t>
+        </is>
+      </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Customer receipts</t>
+          <t>Transfer to payroll</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>11000 Accounts Receivable (A/R)</t>
+          <t>10100 Checking - First Prairie</t>
         </is>
       </c>
       <c r="I16" s="1" t="n">
-        <v>33580.9</v>
+        <v>25000</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>07/08/2026 10:15:00 AM</t>
+          <t>07/01/2026 10:15:00 AM</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -781,60 +813,52 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Total for 1106</t>
+          <t>Total for 1104</t>
         </is>
       </c>
       <c r="H17" s="1" t="n">
-        <v>33580.9</v>
+        <v>25000</v>
       </c>
       <c r="I17" s="1" t="n">
-        <v>33580.9</v>
+        <v>25000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1103</t>
+          <t>1101</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>07/01/2026</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Journal Entry</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>1071</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Cycle Tech Legal</t>
-        </is>
-      </c>
+          <t>Transfer</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Settle distributor dispute (claim from March 2026)</t>
+          <t>Payroll funding</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>68000 Professional Fees</t>
+          <t>10200 Payroll Checking</t>
         </is>
       </c>
       <c r="H19" s="1" t="n">
-        <v>30000</v>
+        <v>40000</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>07/08/2026 10:15:00 AM</t>
+          <t>07/01/2026 10:15:00 AM</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -846,40 +870,32 @@
     <row r="20">
       <c r="B20" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>07/01/2026</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Journal Entry</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>1071</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Cycle Tech Legal</t>
-        </is>
-      </c>
+          <t>Transfer</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Settle distributor dispute (claim from March 2026)</t>
+          <t>Payroll funding</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>20000 Accounts Payable (A/P)</t>
+          <t>10100 Checking - First Prairie</t>
         </is>
       </c>
       <c r="I20" s="1" t="n">
-        <v>30000</v>
+        <v>40000</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>07/08/2026 10:15:00 AM</t>
+          <t>07/01/2026 10:15:00 AM</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -891,60 +907,52 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Total for 1103</t>
+          <t>Total for 1101</t>
         </is>
       </c>
       <c r="H21" s="1" t="n">
-        <v>30000</v>
+        <v>40000</v>
       </c>
       <c r="I21" s="1" t="n">
-        <v>30000</v>
+        <v>40000</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1104</t>
+          <t>1110</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Check</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>4431</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Big Timber Office Supply</t>
-        </is>
-      </c>
+          <t>Deposit</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Supplies</t>
+          <t>Customer receipts</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>67000 Office Supplies</t>
+          <t>10100 Checking - First Prairie</t>
         </is>
       </c>
       <c r="H23" s="1" t="n">
-        <v>2215</v>
+        <v>33580.9</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>07/10/2026 10:15:00 AM</t>
+          <t>07/08/2026 10:15:00 AM</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -956,40 +964,32 @@
     <row r="24">
       <c r="B24" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Check</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>4431</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Big Timber Office Supply</t>
-        </is>
-      </c>
+          <t>Deposit</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Supplies</t>
+          <t>Customer receipts</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>10100 Checking - First Prairie</t>
+          <t>11000 Accounts Receivable (A/R)</t>
         </is>
       </c>
       <c r="I24" s="1" t="n">
-        <v>2215</v>
+        <v>33580.9</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>07/10/2026 10:15:00 AM</t>
+          <t>07/08/2026 10:15:00 AM</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1001,14 +1001,14 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Total for 1104</t>
+          <t>Total for 1110</t>
         </is>
       </c>
       <c r="H25" s="1" t="n">
-        <v>2215</v>
+        <v>33580.9</v>
       </c>
       <c r="I25" s="1" t="n">
-        <v>2215</v>
+        <v>33580.9</v>
       </c>
     </row>
     <row r="26">
@@ -1021,32 +1021,40 @@
     <row r="27">
       <c r="B27" t="inlineStr">
         <is>
-          <t>07/14/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Deposit</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
+          <t>Journal Entry</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>1071</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Cycle Tech Legal</t>
+        </is>
+      </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Customer receipts</t>
+          <t>Settle distributor dispute (claim from March 2026)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>10100 Checking - First Prairie</t>
+          <t>68000 Professional Fees</t>
         </is>
       </c>
       <c r="H27" s="1" t="n">
-        <v>27904.15</v>
+        <v>30000</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>07/14/2026 10:15:00 AM</t>
+          <t>07/08/2026 10:15:00 AM</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -1058,32 +1066,40 @@
     <row r="28">
       <c r="B28" t="inlineStr">
         <is>
-          <t>07/14/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Deposit</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
+          <t>Journal Entry</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>1071</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Cycle Tech Legal</t>
+        </is>
+      </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Customer receipts</t>
+          <t>Settle distributor dispute (claim from March 2026)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>11000 Accounts Receivable (A/R)</t>
+          <t>20000 Accounts Payable (A/P)</t>
         </is>
       </c>
       <c r="I28" s="1" t="n">
-        <v>27904.15</v>
+        <v>30000</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>07/14/2026 10:15:00 AM</t>
+          <t>07/08/2026 10:15:00 AM</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -1099,10 +1115,10 @@
         </is>
       </c>
       <c r="H29" s="1" t="n">
-        <v>27904.15</v>
+        <v>30000</v>
       </c>
       <c r="I29" s="1" t="n">
-        <v>27904.15</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="30">
@@ -1115,7 +1131,7 @@
     <row r="31">
       <c r="B31" t="inlineStr">
         <is>
-          <t>07/15/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1125,7 +1141,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>4433</t>
+          <t>4430</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1135,7 +1151,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>June freight (invoice VF-0630)</t>
+          <t>July freight (VF-0709)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1144,11 +1160,11 @@
         </is>
       </c>
       <c r="H31" s="1" t="n">
-        <v>6100</v>
+        <v>1320</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>07/15/2026 10:15:00 AM</t>
+          <t>07/09/2026 10:15:00 AM</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -1160,7 +1176,7 @@
     <row r="32">
       <c r="B32" t="inlineStr">
         <is>
-          <t>07/15/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1170,7 +1186,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>4433</t>
+          <t>4430</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1180,7 +1196,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>June freight (invoice VF-0630)</t>
+          <t>July freight (VF-0709)</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1189,11 +1205,11 @@
         </is>
       </c>
       <c r="I32" s="1" t="n">
-        <v>6100</v>
+        <v>1320</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>07/15/2026 10:15:00 AM</t>
+          <t>07/09/2026 10:15:00 AM</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -1209,30 +1225,454 @@
         </is>
       </c>
       <c r="H33" s="1" t="n">
-        <v>6100</v>
+        <v>1320</v>
       </c>
       <c r="I33" s="1" t="n">
-        <v>6100</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="H34" s="1" t="n">
-        <v>164800.05</v>
-      </c>
-      <c r="I34" s="1" t="n">
-        <v>164800.05</v>
-      </c>
-    </row>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
+          <t>1108</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>07/10/2026</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>4431</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Big Timber Office Supply</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Supplies</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>67000 Office Supplies</t>
+        </is>
+      </c>
+      <c r="H35" s="1" t="n">
+        <v>2215</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>07/10/2026 10:15:00 AM</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Dana Merritt</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>07/10/2026</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>4431</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Big Timber Office Supply</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Supplies</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>10100 Checking - First Prairie</t>
+        </is>
+      </c>
+      <c r="I36" s="1" t="n">
+        <v>2215</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>07/10/2026 10:15:00 AM</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Dana Merritt</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total for 1108</t>
+        </is>
+      </c>
+      <c r="H37" s="1" t="n">
+        <v>2215</v>
+      </c>
+      <c r="I37" s="1" t="n">
+        <v>2215</v>
+      </c>
+    </row>
     <row r="38">
       <c r="A38" t="inlineStr">
+        <is>
+          <t>1106</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>07/13/2026</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>4432</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Tri-County Tool Rental</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Delivery equipment rental, July</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>66000 Freight Out</t>
+        </is>
+      </c>
+      <c r="H39" s="1" t="n">
+        <v>1150</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>07/13/2026 10:15:00 AM</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Dana Merritt</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>07/13/2026</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>4432</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Tri-County Tool Rental</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Delivery equipment rental, July</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>10100 Checking - First Prairie</t>
+        </is>
+      </c>
+      <c r="I40" s="1" t="n">
+        <v>1150</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>07/13/2026 10:15:00 AM</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Dana Merritt</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Total for 1106</t>
+        </is>
+      </c>
+      <c r="H41" s="1" t="n">
+        <v>1150</v>
+      </c>
+      <c r="I41" s="1" t="n">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>1111</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>07/14/2026</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Deposit</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Customer receipts</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>10100 Checking - First Prairie</t>
+        </is>
+      </c>
+      <c r="H43" s="1" t="n">
+        <v>27904.15</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>07/14/2026 10:15:00 AM</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Dana Merritt</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>07/14/2026</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Deposit</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Customer receipts</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>11000 Accounts Receivable (A/R)</t>
+        </is>
+      </c>
+      <c r="I44" s="1" t="n">
+        <v>27904.15</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>07/14/2026 10:15:00 AM</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Dana Merritt</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total for 1111</t>
+        </is>
+      </c>
+      <c r="H45" s="1" t="n">
+        <v>27904.15</v>
+      </c>
+      <c r="I45" s="1" t="n">
+        <v>27904.15</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>1109</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>07/15/2026</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>4433</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Velo Freight Lines</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>June freight (invoice VF-0630)</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>66000 Freight Out</t>
+        </is>
+      </c>
+      <c r="H47" s="1" t="n">
+        <v>6100</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>07/15/2026 10:15:00 AM</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Dana Merritt</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>07/15/2026</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>4433</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Velo Freight Lines</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>June freight (invoice VF-0630)</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>10100 Checking - First Prairie</t>
+        </is>
+      </c>
+      <c r="I48" s="1" t="n">
+        <v>6100</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>07/15/2026 10:15:00 AM</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Dana Merritt</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Total for 1109</t>
+        </is>
+      </c>
+      <c r="H49" s="1" t="n">
+        <v>6100</v>
+      </c>
+      <c r="I49" s="1" t="n">
+        <v>6100</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="H50" s="1" t="n">
+        <v>175410.05</v>
+      </c>
+      <c r="I50" s="1" t="n">
+        <v>175410.05</v>
+      </c>
+    </row>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="53"/>
+    <row r="54">
+      <c r="A54" t="inlineStr">
         <is>
           <t>Accrual Basis Friday, July 24, 2026 09:05 AM GMTZ</t>
         </is>
